--- a/data/model_ledgers/rainbow-six-tiered-elo.xlsx
+++ b/data/model_ledgers/rainbow-six-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -860,8 +860,1252 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>c673551ee605461b</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>bd90631d6801b264a535824d56d304782bd760573d2d0362da1821b82393b329</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0.643425</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0.023653136882129333</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:33:37.917658Z</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>c29d4e9762ce40fb</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>bd90631d6801b264a535824d56d304782bd760573d2d0362da1821b82393b329</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0.738965</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0.11919313688212929</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:33:38.422983Z</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>e235ca9f8f514768</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>57367e86325a6e95458cb33cc3d225cdf095fb79abd9e22734d81c72b009eaaf</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0.643107</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.033731999999999984</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:38:33.083527Z</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>c42630f316c64e59</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57367e86325a6e95458cb33cc3d225cdf095fb79abd9e22734d81c72b009eaaf</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.738441</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0.13844099999999993</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:38:33.615704Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>12d110f0895e49cc</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>cb82fabd950aa28e9b921f98caa30a4dc8e89636bec11661a64f003e31308bce</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.643032</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.03365700000000005</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:33:27.658950Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>0dc196c2dff04b79</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>cb82fabd950aa28e9b921f98caa30a4dc8e89636bec11661a64f003e31308bce</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.738317</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.1383169999999999</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:33:28.193655Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2c902c6edefb4521</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>a24b6769511bafa4ecf1418d701b77d32fe6e398c06229b42846312dd765a94c</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.642929</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.03355399999999997</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:10:35.608148Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>48e0ed43451d49da</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>a24b6769511bafa4ecf1418d701b77d32fe6e398c06229b42846312dd765a94c</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.738148</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.13814799999999994</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:10:36.337291Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>0a7adbcb8b3743bf</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45f7961dade60be1e8084a40dcc0804f7beb57cb4739e0d686bc14ad3c23b369</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.64291</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.03353499999999998</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:40:13.347708Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>0737167688944c28</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45f7961dade60be1e8084a40dcc0804f7beb57cb4739e0d686bc14ad3c23b369</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.738116</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.1381159999999999</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:40:13.939500Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>b3a45a3b9a6d495f</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5abfbacc5cb76b78275a1604ae93eb223c0b4a7794a63b0d764f8921f60f0e7b</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.642788</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.033413000000000026</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:47:12.403984Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>0.610000</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0.000625</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>0.9615</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:50:10.370946Z</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>5c388706bcf74af3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5abfbacc5cb76b78275a1604ae93eb223c0b4a7794a63b0d764f8921f60f0e7b</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.737915</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.07805105442176863</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:47:12.888957Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ3"/>
+  <autoFilter ref="A1:AJ15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>